--- a/SGI_Sistema-de-gestao-integrado/SGI_Sistema-de-gestao-da-qualidade/Registos_SGQ_Plasticom/SGQ-05_Objetivos_Metas_KPI.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGI_Sistema-de-gestao-da-qualidade/Registos_SGQ_Plasticom/SGQ-05_Objetivos_Metas_KPI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGI_Sistema-de-gestao-da-qualidade\Registos_SGQ_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6291CE2-F1CE-45E6-A4AA-69022693A7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8CF0722-74E7-48A3-9EA8-722528510B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3679,7 +3679,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-158D-4BA2-BC48-79DD9E84C50C}"/>
+              <c16:uniqueId val="{00000000-0011-49C2-AC36-5D8FA04D2871}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3922,7 +3922,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AE5C-4FD9-83FC-A6980205714C}"/>
+              <c16:uniqueId val="{00000000-3FCC-433F-A90D-618FD496E293}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
